--- a/Existing_tools_summary.xlsx
+++ b/Existing_tools_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/taouk_m_unimelb_edu_au/Documents/2025(Ingle_Postdoc)/ONT_read_simulator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/taouk_m_unimelb_edu_au/Documents/2025(Ingle_Postdoc)/ONT_read_simulator/ONT-Read-Simulator-Benchmarking/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="579" documentId="8_{C8605B36-6344-D34A-ADA9-903E0E46C7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18E38E21-366F-2F45-B3E3-5F403797CCBF}"/>
   <bookViews>
-    <workbookView xWindow="23080" yWindow="6340" windowWidth="28060" windowHeight="13700" xr2:uid="{16E25D12-CE4A-C943-AB08-26F50A53FAC0}"/>
+    <workbookView xWindow="35360" yWindow="3720" windowWidth="28060" windowHeight="13700" xr2:uid="{16E25D12-CE4A-C943-AB08-26F50A53FAC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -911,7 +911,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -947,9 +947,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1438,9 +1437,8 @@
       <c r="L4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="37"/>
       <c r="N4" s="27"/>
-      <c r="O4" s="38"/>
+      <c r="O4" s="37"/>
     </row>
     <row r="5" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="34" t="s">
@@ -1476,9 +1474,8 @@
       <c r="L5" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="37"/>
       <c r="N5" s="27"/>
-      <c r="O5" s="38"/>
+      <c r="O5" s="37"/>
     </row>
     <row r="6" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="34" t="s">
@@ -1512,13 +1509,13 @@
         <v>41</v>
       </c>
       <c r="L6" s="15"/>
-      <c r="M6" s="37" t="s">
+      <c r="M6" t="s">
         <v>149</v>
       </c>
       <c r="N6" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="O6" s="38" t="s">
+      <c r="O6" s="37" t="s">
         <v>165</v>
       </c>
     </row>
@@ -1556,13 +1553,13 @@
       <c r="L7" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" t="s">
         <v>150</v>
       </c>
       <c r="N7" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="O7" s="38" t="s">
+      <c r="O7" s="37" t="s">
         <v>168</v>
       </c>
     </row>
@@ -1600,9 +1597,8 @@
       <c r="L8" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="37"/>
       <c r="N8" s="27"/>
-      <c r="O8" s="38"/>
+      <c r="O8" s="37"/>
     </row>
     <row r="9" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="34" t="s">
@@ -1638,9 +1634,8 @@
       <c r="L9" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="37"/>
       <c r="N9" s="27"/>
-      <c r="O9" s="38"/>
+      <c r="O9" s="37"/>
     </row>
     <row r="10" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="34" t="s">
@@ -1674,9 +1669,8 @@
         <v>77</v>
       </c>
       <c r="L10" s="15"/>
-      <c r="M10" s="37"/>
       <c r="N10" s="27"/>
-      <c r="O10" s="38"/>
+      <c r="O10" s="37"/>
     </row>
     <row r="11" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="34" t="s">
@@ -1710,13 +1704,13 @@
         <v>84</v>
       </c>
       <c r="L11" s="15"/>
-      <c r="M11" s="37" t="s">
+      <c r="M11" t="s">
         <v>151</v>
       </c>
       <c r="N11" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="O11" s="38" t="s">
+      <c r="O11" s="37" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1730,7 +1724,7 @@
       <c r="D12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" t="s">
         <v>88</v>
       </c>
       <c r="F12" s="18" t="s">
@@ -1745,7 +1739,7 @@
       <c r="I12" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" t="s">
         <v>91</v>
       </c>
       <c r="K12" s="15" t="s">
@@ -1754,9 +1748,8 @@
       <c r="L12" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="M12" s="37"/>
       <c r="N12" s="27"/>
-      <c r="O12" s="38"/>
+      <c r="O12" s="37"/>
     </row>
     <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="34" t="s">
@@ -1792,13 +1785,13 @@
       <c r="L13" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" t="s">
         <v>157</v>
       </c>
       <c r="N13" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="O13" s="38" t="s">
+      <c r="O13" s="37" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1834,13 +1827,13 @@
         <v>111</v>
       </c>
       <c r="L14" s="15"/>
-      <c r="M14" s="37" t="s">
+      <c r="M14" t="s">
         <v>152</v>
       </c>
       <c r="N14" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="O14" s="38" t="s">
+      <c r="O14" s="37" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1876,18 +1869,18 @@
         <v>114</v>
       </c>
       <c r="L15" s="15"/>
-      <c r="M15" s="37" t="s">
+      <c r="M15" t="s">
         <v>153</v>
       </c>
       <c r="N15" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="O15" s="38" t="s">
+      <c r="O15" s="37" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>115</v>
       </c>
       <c r="C16" s="20" t="s">
@@ -1920,18 +1913,18 @@
       <c r="L16" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M16" t="s">
         <v>154</v>
       </c>
       <c r="N16" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="O16" s="38" t="s">
+      <c r="O16" s="37" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="38" t="s">
         <v>119</v>
       </c>
       <c r="C17" s="20" t="s">
@@ -1964,47 +1957,46 @@
       <c r="L17" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="M17" s="37"/>
       <c r="N17" s="27"/>
-      <c r="O17" s="38"/>
+      <c r="O17" s="37"/>
     </row>
     <row r="18" spans="2:15" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="42">
         <v>2023</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="43">
         <v>45864</v>
       </c>
-      <c r="I18" s="42" t="s">
+      <c r="I18" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="K18" s="42" t="s">
+      <c r="K18" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="L18" s="42" t="s">
+      <c r="L18" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="45"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="47"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="46"/>
     </row>
     <row r="19" spans="2:15" ht="16" x14ac:dyDescent="0.2">
       <c r="G19" s="1"/>
